--- a/data/daily/2026-09/2026-09-11.xlsx
+++ b/data/daily/2026-09/2026-09-11.xlsx
@@ -1195,14 +1195,39 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="342900" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1217,17 +1242,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="342900" cy="457200"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1242,17 +1267,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="361950" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1267,17 +1292,17 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="381000" cy="457200"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1292,35 +1317,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>6</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="342900" cy="457200"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
       <row>7</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="342900" cy="457200"/>
+    <ext cx="381000" cy="457200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1450,27 +1450,52 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="933450" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>4</col>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1478,104 +1503,79 @@
     <ext cx="933450" cy="1238250"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>6</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>7</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>7</col>
+    <ext cx="1028700" cy="1238250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="933450" cy="1238250"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>8</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="933450" cy="1238250"/>
+    <ext cx="1028700" cy="1238250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 예쁜 포장과 알찬 구성으로 선물 시 받는 사람의 만족도가 높음</t>
+          <t>선물용으로 좋은 구성 — 예쁜 포장과 정성스러운 패키지 구성으로 선물하기에 매우 적합함</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>편하게 섭취 가능한 제형 — 액상과 알약을 함께 간편하고 맛있게 먹을 수 있음</t>
+          <t>피로 회복 및 건강 증진 — 섭취 후 감기 기운이 완화되고 피로가 풀리며 기운이 나는 효과를 체감함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>체력 회복 및 피로 개선 — 섭취 후 기운이 나고 피로 회복과 감기 증상 완화에 도움이 됨</t>
+          <t>편리한 액상·알약 섭취 — 알약과 액상 제형을 한 번에 편하게 복용할 수 있어 유용함</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -2659,25 +2659,29 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>피로 해소 및 체력 증진 — 섭취 후 오후 피로감이 줄어들고 버티는 힘이 생김</t>
+          <t>피로 개선 및 체력 증진 — 오후 피로감이 줄어들고 힘든 상황에서 체력 유지에 도움을 줌</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>정성스러운 선물용 패키지 — 아담한 포장과 쇼핑백이 함께 제공되어 선물하기에 적합함</t>
+          <t>목 넘김이 수월한 알약 — 알약 크기가 목 넘기기에 부담 없어 편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>편안한 알약 목넘김 — 알약 크기가 목을 넘기기에 부담이 없고 먹기 편리함</t>
+          <t>선물에 적합한 패키지 — 쇼핑백이 함께 구성되어 있고 귀여운 상자로 선물용 만족도가 높음</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>배송 중 포장재 파손 — 배송 과정에서 선물 박스가 파손되어 전달됨</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
+          <t>파손된 배송 상태 — 배송 과정에서 선물 박스가 파손된 상태로 도착하여 배송관리가 필요함</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>호불호 갈리는 맛 — 맛이 아주 뛰어난 편은 아니나 참고 먹을 만한 수준임</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
@@ -2722,22 +2726,22 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 하루 종일 일해도 아침에 가뿐하고 피로감이 많이 해소됨</t>
+          <t>피로 회복 효과 체감 — 지속되던 피로감이 줄고 아침에 일어날 때 가뿐한 느낌을 받음</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>고급스러운 포장 상태 — 패키지가 고급스럽게 포장되어 도착하여 선물용으로 좋음</t>
+          <t>고급스러운 포장 상태 — 포장이 깔끔하고 고급스럽게 되어 있어 선물용 및 선물 받기에 양호함</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>맛있고 간편한 복용 — 맛이 좋아 섭취 부담이 없고 먹기 편리함</t>
+          <t>맛과 복용의 편의성 — 맛이 양호하며 복용 방법이 간편하여 매일 챙겨 먹기 용이함</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>기저질환자 섭취 주의 — 당뇨 등 기저질환이 있는 경우 직접 복용하기에 부담이 있음</t>
+          <t>당뇨 환자 섭취 주의 — 당 함유 문제로 당뇨가 있는 경우 직접 복용하기 어려울 수 있음</t>
         </is>
       </c>
       <c r="O4" t="inlineStr"/>
@@ -2785,17 +2789,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>올인원 섭취의 간편함 — 여러 영양제를 따로 먹지 않고 한 번에 간편하게 챙길 수 있음</t>
+          <t>간편한 올인원 섭취 — 따로 챙겨 먹기 번거로운 영양제를 한 번에 간편하게 섭취 가능함</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>피로 회복 및 체력 증진 — 힘들 때 먹으면 체력이 회복되고 피로가 덜한 느낌을 받음</t>
+          <t>넉넉한 증정 구성 — 카카오 단독 2입 추가 증정 혜택이 있어 풍성하게 느껴짐</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>알찬 혜택과 뛰어난 휴대성 — 추가 증정 구성이 알차고 가방에 쏙 들어가는 크기로 휴대하기 좋음</t>
+          <t>피로 회복 및 휴대성 — 가방에 들어가는 사이즈로 휴대가 편하고 피로 회복 체감이 양호함</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -2844,22 +2848,18 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 젤리 — 상큼하고 쫄깃하여 부담 없이 맛있게 먹기 좋은 젤리 형태임</t>
+          <t>맛있는 젤리 제형 — 상큼하고 쫄깃하여 맛있는 건강식품으로 부담 없이 먹기 좋음</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>활력 충전 및 기분 전환 — 부담 없이 먹으며 비타민을 충전하고 활력을 얻을 수 있음</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>귀여운 증정품 포함 — 함께 구성된 로고 키캡이 귀엽고 소장 가치가 있음</t>
-        </is>
-      </c>
+          <t>센스 있는 구성품 — 포장이 귀엽고 키캡 등 마음에 드는 굿즈가 동봉되어 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>아쉬운 젤리 식감 — 젤리의 식감이 조금 단단하여 더 말랑했으면 하는 아쉬움이 있음</t>
+          <t>아쉬운 젤리 식감 — 젤리가 다소 딱딱한 편이라 조금 더 말랑했으면 하는 아쉬움이 있음</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -2907,17 +2907,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 효과 — 지치고 피로할 때 먹으면 효과가 빠르게 체감됨</t>
+          <t>뛰어난 피로 회복 — 피로감을 자주 느끼던 상태에서 섭취 시 활력이 생기고 효과가 좋음</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>간편한 휴대 및 마시는 제형 — 한 병씩 들고 다니며 마실 수 있어 출근길이나 외출 시 간편함</t>
+          <t>우수한 휴대성 및 편의성 — 한 병씩 들고 다니며 마시기 편해서 출근길 등에 챙기기 용이함</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>맛있고 부담 없는 섭취 — 맛이 좋아서 온 가족이 원샷으로 부담 없이 먹을 수 있음</t>
+          <t>맛과 빠른 배송 — 배송이 빠르고 섭취 시 맛도 양호하여 온 가족이 마시기 적합함</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -2966,17 +2966,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>예쁜 선물용 포장 — 선물 포장이 이쁘게 되어 있어 주고받기 부담스럽지 않음</t>
+          <t>선물용 예쁜 포장 — 선물 포장이 이쁘게 되어 있어 선물용으로 주고받기 부담 없고 좋음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>체력 충전 및 건강 증진 — 힘들 때 먹으면 힘이 나고 건강해지는 느낌을 받음</t>
+          <t>빠른 배송 및 편의성 — 배송이 빠르며 하루 하나씩 섭취하기 편하게 구성됨</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>간편한 복용과 빠른 배송 — 먹기가 편리하며 배송이 빠르게 도착함</t>
+          <t>컨디션 관리 효과 — 힘들 때 복용하면 힘이 나고 건강해지는 기분을 얻을 수 있음</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -3025,24 +3025,20 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>간편한 원스탑 섭취 방식 — 눌러서 가루를 내려 섞어 마시는 신기하고 간편한 형태임</t>
+          <t>간편한 원스탑 섭취 — 눌러서 분말과 액상을 섞어 바로 마시는 방식이라 편하고 신기함</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>음료 같은 상큼한 맛 — 약 같지 않고 음료수처럼 맛있게 복용할 수 있음</t>
+          <t>고급스러운 패키지 — 포장이 고급스럽고 추가 증정 구성으로 알차게 느껴짐</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>고급스러운 포장 디자인 — 패키지가 예쁘고 고급스러워 선물용으로 아주 적합함</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>생각보다 큰 제품 용기 — 제품의 실물 크기가 생각했던 것보다 다소 큼</t>
-        </is>
-      </c>
+          <t>피로 회복 및 좋은 맛 — 음료수처럼 맛이 좋고 피로할 때 컨디션 개선에 도움이 됨</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
     </row>
@@ -3088,22 +3084,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 구성 — 추석 패키지와 동봉된 젤리 구성이 정성스럽고 감동적임</t>
+          <t>고급스러운 선물 포장 — 선물 패키지가 고급스럽고 귀여워서 받는 사람이 만족해함</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>피로 해소 도움 체감 — 피곤할 때 하나씩 먹으면 몸이 좋아하는 것이 느껴지고 피로감이 덜함</t>
+          <t>빠른 배송 및 편의성 — 배송이 빠르고 피곤할 때 하나씩 꺼내 간편하게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>빠른 배송 및 편리함 — 배송이 빠르고 매일 간편하게 챙겨 먹기 좋음</t>
+          <t>피로 회복 체감 효과 — 매일 섭취 시 피로감이 줄어들고 체력이 보충되는 느낌을 받음</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>아쉬운 제품 수량 — 지속적으로 복용하기에 수량이 다소 부족하게 느껴짐</t>
+          <t>용량 부족의 아쉬움 — 꾸준한 건강 관리를 위해 더 많은 수량이 필요하게 느껴짐</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -3151,17 +3147,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>한 번에 챙기는 영양 케어 — 필요한 영양소를 한 번에 케어할 수 있어 중년 남성 필수템임</t>
+          <t>깔끔한 선물 포장 — 포장이 깔끔하고 성의 있어 보여 선물용으로 매우 만족스러움</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>편리한 휴대 및 섭취 — 하루 하나씩 들고 다니며 먹기 쉽고 섭취가 간편함</t>
+          <t>우수한 휴대성 및 편의성 — 하루 하나씩 먹기 편하고 휴대성이 뛰어나 관리하기 쉬움</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>고급스러운 디자인 포장 — 포장 디자인이 만족스러워 선물받은 느낌을 줌</t>
+          <t>피로 회복 체감 효과 — 필수 영양소를 한 번에 챙겨 피로함이 덜해지는 느낌을 받음</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -3210,20 +3206,24 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>뛰어난 콜라보 굿즈 구성 — 포토카드, 엽서 등 굿즈 퀄리티가 훌륭하여 소장 가치가 높음</t>
+          <t>소장 가치 높은 구성 — 콜라보 굿즈인 포토카드와 엽서 구성이 훌륭하여 소장 가치가 높음</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>맛있는 베리말차 라떼 맛 — 우유에 섞으면 딸기말차라떼처럼 맛있고 간편하게 즐길 수 있음</t>
+          <t>훌륭한 맛 및 활용성 — 말차에 딸기향이 나며 우유와 섞어 딸기말차라떼처럼 먹을 수 있음</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>풍성한 사은품 혜택 — 고단백질바 등 다양한 구성품을 함께 챙겨주어 만족스러움</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>빠른 배송 및 사은품 — 굿즈 구김 없이 배송 상태가 양호하며 단백질바 증정 혜택도 만족스러움</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>굿즈 중심 구매 목적 — 효소 섭취보다는 굿즈 소장이 주 목적인 경우가 있음</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
     </row>
@@ -3269,22 +3269,22 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>매우 고급스러운 포장 — 은은하고 고급스러운 색상의 포장으로 선물 가치가 높음</t>
+          <t>고급스러운 예쁜 포장 — 은은한 핑크 색상과 오간자 포장이 매우 고급스러워 선물용으로 훌륭함</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>피부 상태 개선 체감 — 복용 후 피부가 한결 맑아지는 듯한 느낌을 체감함</t>
+          <t>피부 개선 체감 — 꾸준히 먹어보니 피부가 맑아지는 것 같은 느낌을 받음</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>알찬 샘플 추가 구성 — 본품 외에 추가 샘플이 증정되어 만족도가 높음</t>
+          <t>샘플 증정 구성 — 추가 샘플 구성이 함께 포함되어 만족스러운 혜택을 제공함</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>즉각적 효과 확인의 한계 — 복용 초반에는 효과를 즉시 체감하기 어려움</t>
+          <t>단기간 효과 체감 미흡 — 섭취한 지 며칠 지나지 않아 즉각적인 효과 체감은 아직 어려움</t>
         </is>
       </c>
       <c r="O13" t="inlineStr"/>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 패키지 — 저렴한 가격에 풍성한 수량을 구매할 수 있어 경제적임</t>
+          <t>훌륭한 가성비와 맛 — 저렴한 가격 대비 다양한 양념과 뻑뻑하지 않은 맛으로 만족스러움</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>질리지 않는 다양한 맛 — 메뉴가 다채롭고 양념이 자극적이지 않아 매일 먹기 좋음</t>
+          <t>간편한 전자레인지 조리 — 전자레인지 조리로 간편하게 식단 관리를 진행할 수 있음</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>간편한 전자레인지 조리 — 전자레인지 조리로 다이어트 식단을 간편하게 해결할 수 있음</t>
+          <t>빠른 배송과 꼼꼼 포장 — 배송이 빠르고 꼼꼼하게 포장되어 지속적으로 재구매함</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>배송 중 제품 해동 — 배송 시 제품이 완전히 녹아 도착하는 문제가 있음</t>
+          <t>제품 해동 배송 문제 — 배송 중 포장 내 제품이 전체적으로 녹아서 도착함</t>
         </is>
       </c>
       <c r="O14" t="inlineStr"/>
@@ -3395,17 +3395,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 비리고 텁텁한 맛없이 일반 모카라떼나 초코우유처럼 맛있음</t>
+          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 비리거나 텁텁한 맛없이 부드럽게 넘어감</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>부드러운 목넘김과 속 편안함 — 목넘김이 부드럽고 복용 후 속이 더부룩하지 않음</t>
+          <t>운동 후 포만감 및 영양 — 운동 후 단백질 보충용으로 좋고 속이 더부룩하지 않으며 허기 완화에 도움 됨</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>휴대하기 편한 슬림 패키지 — 패키지가 슬림하여 가방에 넣어 다니며 챙겨 마시기 유용함</t>
+          <t>우수한 휴대성 및 배송 — 슬림한 패키지로 들고 다니기 편하며 배송이 빠르게 진행됨</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -3454,22 +3454,22 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>골라 먹는 다채로운 종류 — 다양한 종류로 구성되어 하나씩 골라 먹는 재미가 있음</t>
+          <t>다양한 종류와 뛰어난 맛 — 여러 맛이 구성되어 골라 먹는 재미가 있고 닭가슴살 맛이 좋음</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>합리적인 할인 가격 — 알찬 패키지 구성을 저렴한 세일 가격으로 구매 가능함</t>
+          <t>풍성한 할인 및 혜택 — 할인 가격과 보냉 파우치 증정 구성으로 가성비가 훌륭함</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>유용한 보냉파우치 증정 — 증정되는 보냉백이 도시락을 싸 다닐 때 요용함</t>
+          <t>간편한 식단 관리 — 아침이나 점심 도시락 대용으로 간편히 식단 관리가 가능함</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>배송 시 상품 해동 문제 — 도착했을 때 제품이 많이 녹아 있는 경우가 있음</t>
+          <t>제품 해동 및 배송 문의 — 여름철 배송 시 많이 녹아서 오거나 사은품 별도 배송 여부 확인 필요함</t>
         </is>
       </c>
       <c r="O16" t="inlineStr"/>
@@ -3478,7 +3478,7 @@
     <row r="17" ht="38" customHeight="1">
       <c r="B17" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3486,48 +3486,48 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>삼대오백</t>
+          <t>그레인온</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>17,900원</t>
+          <t>46,900원</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/6352718</t>
+          <t>https://gift.kakao.com/product/13180343</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260831160758_47e2ca88a3ec4835979cf9737a40b276.jpg</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>1899</v>
+        <v>1654</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>귀여운 키링 증정 혜택 — 함께 구성된 키링 증정품의 만족도가 매우 높음</t>
+          <t>소화 및 배변 활동 개선 — 식후 속 더부룩함이 감소하고 배변 활동을 원활하게 도와줌</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>물이나 음료에 잘 섞임 — 물이나 음료에 타서 먹기 부담이 없고 간편함</t>
+          <t>고소한 군고구마 맛 — 군고구마 맛이 나며 고소하여 거부감 없이 맛있게 먹을 수 있음</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>체감되는 운동 및 근육 효과 — 지속 섭취 시 몸이 커지고 득근하는 효과를 느낌</t>
+          <t>간편한 스틱 및 혜택 — 1포씩 개별 포장되어 간편하며 할인 이벤트 및 사은품 구성이 알참</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
     <row r="18" ht="38" customHeight="1">
       <c r="B18" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3545,48 +3545,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
+          <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>그레인온</t>
+          <t>삼대오백</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46,900원</t>
+          <t>17,900원</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://gift.kakao.com/product/13180343</t>
+          <t>https://gift.kakao.com/product/6352718</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://st.kakaocdn.net/product/gift/product/20260831160758_47e2ca88a3ec4835979cf9737a40b276.jpg</t>
+          <t>https://st.kakaocdn.net/product/gift/product/20260910161018_5069f5d0428843148af2cd85fc6be74f.jpg</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>1654</v>
+        <v>1899</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>고소한 군고구마 맛 — 군고구마 맛이 나며 부담 없이 맛있게 먹을 수 있음</t>
+          <t>섭취 편의성과 효과 — 물이나 음료에 쉽게 타 먹을 수 있고 운동 시 수행 능력 및 득근에 도움 됨</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>속 편한 소화 및 배변 도움 — 식후 더부룩함과 답답함이 줄어들고 배변 활동에 도움이 됨</t>
+          <t>귀여운 키링 증정 — 함께 제공되는 캐릭터 키링 사은품에 대한 만족도가 높음</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>간편한 스틱 포장 — 한 포씩 포장되어 있어 가지고 다니며 챙겨 먹기 편함</t>
+          <t>입문용 적합 용량 — 크레아틴을 처음 먹어보는 사람도 부담 없이 시작하기에 적절한 용량임</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -3635,17 +3635,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>확실한 활력 및 체력 증진 — 초고함량 아르기닌 섭취로 체력, 지구력, 집중력 향상에 도움 됨</t>
+          <t>초고함량 및 우수한 효과 — 1포당 L-아르기닌 6,200mg 함유로 운동 및 일상 활력 증진에 효과적임</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>편리한 1포 개별 포장 — 개별 포장되어 있어 휴대가 쉽고 하루 1포로 간편하게 섭취함</t>
+          <t>고급스러운 포장 패키지 — 블랙앤레드 패키지와 전용 쇼핑백, 추가 덤 증정으로 선물용으로 우수함</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>선물용으로 우수한 패키지 — 고급스러운 포장 디자인과 쇼핑백이 함께 제공되어 선물용으로 제격임</t>
+          <t>간편한 개별 포장 — 하루 1포 스틱 제형으로 개별 포장되어 휴대가 편하고 복용이 간단함</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -3694,17 +3694,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>체감되는 일상 피로 해소 — 섭취 후 아침에 몸이 가볍고 일상 피로가 줄어듦</t>
+          <t>챙겨 먹기 편한 알약 — 알약 제형으로 제작되어 매일 간편하게 영양을 챙길 수 있음</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>간편한 알약 제형 — 알약 형태로 되어 있어 매일 부담 없이 챙겨 먹기 편리함</t>
+          <t>시너지 알찬 구성 — 아르기닌과 밀크씨슬(마카) 조합으로 피로 완화 및 활력 관리에 유용함</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>알찬 2개월분 세트 구성 — 아르기닌과 밀크씨슬(마카) 조합의 넉넉한 2개월분 구성이 만족스러움</t>
+          <t>선물용 고급 쇼핑백 — 쇼핑백이 함께 포함되어 정성스러운 건강 선물용으로 적합함</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -3753,17 +3753,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>피로 회복 및 운동 지원 — 아침 공복에 복용 시 가벼운 느낌이 들고 피로 회복과 운동에 도움이 됨</t>
+          <t>간편한 액상 스틱 — 액상 타입 스틱으로 물에 타 먹기 편하고 외출 시 휴대가 용이함</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>부담 없는 레몬맛 액상 — 상큼한 레몬맛 액상이라 물에 타 먹거나 그냥 먹기 부담 없음</t>
+          <t>상큼한 레몬 맛 — 레몬 맛으로 구성되어 거부감 없이 맛있게 복용 가능함</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>외출 시 용이한 휴대성 — 액상 스틱 타입으로 외출할 때 간편히 챙기기 좋음</t>
+          <t>활력 증진 및 피로 회복 — 아침 공복이나 운동 전에 먹으면 피로 회복과 에너지를 얻는 느낌임</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -4126,76 +4126,75 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>선물용으로 높은 만족도 — 예쁜 포장과 알찬 구성으로 선물 시 받는 사람의 만족도가 높음
-편하게 섭취 가능한 제형 — 액상과 알약을 함께 간편하고 맛있게 먹을 수 있음
-체력 회복 및 피로 개선 — 섭취 후 기운이 나고 피로 회복과 감기 증상 완화에 도움이 됨</t>
+          <t>선물용으로 좋은 구성 — 예쁜 포장과 정성스러운 패키지 구성으로 선물하기에 매우 적합함
+피로 회복 및 건강 증진 — 섭취 후 감기 기운이 완화되고 피로가 풀리며 기운이 나는 효과를 체감함
+편리한 액상·알약 섭취 — 알약과 액상 제형을 한 번에 편하게 복용할 수 있어 유용함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>피로 해소 및 체력 증진 — 섭취 후 오후 피로감이 줄어들고 버티는 힘이 생김
-정성스러운 선물용 패키지 — 아담한 포장과 쇼핑백이 함께 제공되어 선물하기에 적합함
-편안한 알약 목넘김 — 알약 크기가 목을 넘기기에 부담이 없고 먹기 편리함</t>
+          <t>피로 개선 및 체력 증진 — 오후 피로감이 줄어들고 힘든 상황에서 체력 유지에 도움을 줌
+목 넘김이 수월한 알약 — 알약 크기가 목 넘기기에 부담 없어 편하게 섭취 가능함
+선물에 적합한 패키지 — 쇼핑백이 함께 구성되어 있고 귀여운 상자로 선물용 만족도가 높음</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 피로 회복 효과 — 하루 종일 일해도 아침에 가뿐하고 피로감이 많이 해소됨
-고급스러운 포장 상태 — 패키지가 고급스럽게 포장되어 도착하여 선물용으로 좋음
-맛있고 간편한 복용 — 맛이 좋아 섭취 부담이 없고 먹기 편리함</t>
+          <t>피로 회복 효과 체감 — 지속되던 피로감이 줄고 아침에 일어날 때 가뿐한 느낌을 받음
+고급스러운 포장 상태 — 포장이 깔끔하고 고급스럽게 되어 있어 선물용 및 선물 받기에 양호함
+맛과 복용의 편의성 — 맛이 양호하며 복용 방법이 간편하여 매일 챙겨 먹기 용이함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>올인원 섭취의 간편함 — 여러 영양제를 따로 먹지 않고 한 번에 간편하게 챙길 수 있음
-피로 회복 및 체력 증진 — 힘들 때 먹으면 체력이 회복되고 피로가 덜한 느낌을 받음
-알찬 혜택과 뛰어난 휴대성 — 추가 증정 구성이 알차고 가방에 쏙 들어가는 크기로 휴대하기 좋음</t>
+          <t>간편한 올인원 섭취 — 따로 챙겨 먹기 번거로운 영양제를 한 번에 간편하게 섭취 가능함
+넉넉한 증정 구성 — 카카오 단독 2입 추가 증정 혜택이 있어 풍성하게 느껴짐
+피로 회복 및 휴대성 — 가방에 들어가는 사이즈로 휴대가 편하고 피로 회복 체감이 양호함</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>상큼하고 맛있는 젤리 — 상큼하고 쫄깃하여 부담 없이 맛있게 먹기 좋은 젤리 형태임
-활력 충전 및 기분 전환 — 부담 없이 먹으며 비타민을 충전하고 활력을 얻을 수 있음
-귀여운 증정품 포함 — 함께 구성된 로고 키캡이 귀엽고 소장 가치가 있음</t>
+          <t>맛있는 젤리 제형 — 상큼하고 쫄깃하여 맛있는 건강식품으로 부담 없이 먹기 좋음
+센스 있는 구성품 — 포장이 귀엽고 키캡 등 마음에 드는 굿즈가 동봉되어 만족도가 높음</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>확실한 피로 개선 효과 — 지치고 피로할 때 먹으면 효과가 빠르게 체감됨
-간편한 휴대 및 마시는 제형 — 한 병씩 들고 다니며 마실 수 있어 출근길이나 외출 시 간편함
-맛있고 부담 없는 섭취 — 맛이 좋아서 온 가족이 원샷으로 부담 없이 먹을 수 있음</t>
+          <t>뛰어난 피로 회복 — 피로감을 자주 느끼던 상태에서 섭취 시 활력이 생기고 효과가 좋음
+우수한 휴대성 및 편의성 — 한 병씩 들고 다니며 마시기 편해서 출근길 등에 챙기기 용이함
+맛과 빠른 배송 — 배송이 빠르고 섭취 시 맛도 양호하여 온 가족이 마시기 적합함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>예쁜 선물용 포장 — 선물 포장이 이쁘게 되어 있어 주고받기 부담스럽지 않음
-체력 충전 및 건강 증진 — 힘들 때 먹으면 힘이 나고 건강해지는 느낌을 받음
-간편한 복용과 빠른 배송 — 먹기가 편리하며 배송이 빠르게 도착함</t>
+          <t>선물용 예쁜 포장 — 선물 포장이 이쁘게 되어 있어 선물용으로 주고받기 부담 없고 좋음
+빠른 배송 및 편의성 — 배송이 빠르며 하루 하나씩 섭취하기 편하게 구성됨
+컨디션 관리 효과 — 힘들 때 복용하면 힘이 나고 건강해지는 기분을 얻을 수 있음</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>간편한 원스탑 섭취 방식 — 눌러서 가루를 내려 섞어 마시는 신기하고 간편한 형태임
-음료 같은 상큼한 맛 — 약 같지 않고 음료수처럼 맛있게 복용할 수 있음
-고급스러운 포장 디자인 — 패키지가 예쁘고 고급스러워 선물용으로 아주 적합함</t>
+          <t>간편한 원스탑 섭취 — 눌러서 분말과 액상을 섞어 바로 마시는 방식이라 편하고 신기함
+고급스러운 패키지 — 포장이 고급스럽고 추가 증정 구성으로 알차게 느껴짐
+피로 회복 및 좋은 맛 — 음료수처럼 맛이 좋고 피로할 때 컨디션 개선에 도움이 됨</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>고급스러운 패키지 구성 — 추석 패키지와 동봉된 젤리 구성이 정성스럽고 감동적임
-피로 해소 도움 체감 — 피곤할 때 하나씩 먹으면 몸이 좋아하는 것이 느껴지고 피로감이 덜함
-빠른 배송 및 편리함 — 배송이 빠르고 매일 간편하게 챙겨 먹기 좋음</t>
+          <t>고급스러운 선물 포장 — 선물 패키지가 고급스럽고 귀여워서 받는 사람이 만족해함
+빠른 배송 및 편의성 — 배송이 빠르고 피곤할 때 하나씩 꺼내 간편하게 먹을 수 있음
+피로 회복 체감 효과 — 매일 섭취 시 피로감이 줄어들고 체력이 보충되는 느낌을 받음</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>한 번에 챙기는 영양 케어 — 필요한 영양소를 한 번에 케어할 수 있어 중년 남성 필수템임
-편리한 휴대 및 섭취 — 하루 하나씩 들고 다니며 먹기 쉽고 섭취가 간편함
-고급스러운 디자인 포장 — 포장 디자인이 만족스러워 선물받은 느낌을 줌</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>깔끔한 선물 포장 — 포장이 깔끔하고 성의 있어 보여 선물용으로 매우 만족스러움
+우수한 휴대성 및 편의성 — 하루 하나씩 먹기 편하고 휴대성이 뛰어나 관리하기 쉬움
+피로 회복 체감 효과 — 필수 영양소를 한 번에 챙겨 피로함이 덜해지는 느낌을 받음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
@@ -4204,30 +4203,27 @@
       <c r="C9" s="3" t="inlineStr"/>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>배송 중 포장재 파손 — 배송 과정에서 선물 박스가 파손되어 전달됨</t>
+          <t>파손된 배송 상태 — 배송 과정에서 선물 박스가 파손된 상태로 도착하여 배송관리가 필요함
+호불호 갈리는 맛 — 맛이 아주 뛰어난 편은 아니나 참고 먹을 만한 수준임</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>기저질환자 섭취 주의 — 당뇨 등 기저질환이 있는 경우 직접 복용하기에 부담이 있음</t>
+          <t>당뇨 환자 섭취 주의 — 당 함유 문제로 당뇨가 있는 경우 직접 복용하기 어려울 수 있음</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 젤리 식감 — 젤리의 식감이 조금 단단하여 더 말랑했으면 하는 아쉬움이 있음</t>
+          <t>아쉬운 젤리 식감 — 젤리가 다소 딱딱한 편이라 조금 더 말랑했으면 하는 아쉬움이 있음</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>생각보다 큰 제품 용기 — 제품의 실물 크기가 생각했던 것보다 다소 큼</t>
-        </is>
-      </c>
+      <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 제품 수량 — 지속적으로 복용하기에 수량이 다소 부족하게 느껴짐</t>
+          <t>용량 부족의 아쉬움 — 꾸준한 건강 관리를 위해 더 많은 수량이 필요하게 느껴짐</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -4453,12 +4449,12 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -4510,12 +4506,12 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
+          <t>그레인온</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
           <t>삼대오백</t>
-        </is>
-      </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>그레인온</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -4567,12 +4563,12 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
+          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
           <t>[운동선물/헬스] 삼대오백 모노 크레아틴 100서빙 운동 필수템</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>[그레인온] 골드 카무트 브랜드밀 효소 3개월(+선물포장) +파로저당 단백칩 증정</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -4650,10 +4646,10 @@
         <v>142</v>
       </c>
       <c r="H19" s="3" t="n">
+        <v>1654</v>
+      </c>
+      <c r="I19" s="3" t="n">
         <v>1899</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>1654</v>
       </c>
       <c r="J19" s="3" t="n">
         <v>248</v>
@@ -4673,72 +4669,72 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>뛰어난 콜라보 굿즈 구성 — 포토카드, 엽서 등 굿즈 퀄리티가 훌륭하여 소장 가치가 높음
-맛있는 베리말차 라떼 맛 — 우유에 섞으면 딸기말차라떼처럼 맛있고 간편하게 즐길 수 있음
-풍성한 사은품 혜택 — 고단백질바 등 다양한 구성품을 함께 챙겨주어 만족스러움</t>
+          <t>소장 가치 높은 구성 — 콜라보 굿즈인 포토카드와 엽서 구성이 훌륭하여 소장 가치가 높음
+훌륭한 맛 및 활용성 — 말차에 딸기향이 나며 우유와 섞어 딸기말차라떼처럼 먹을 수 있음
+빠른 배송 및 사은품 — 굿즈 구김 없이 배송 상태가 양호하며 단백질바 증정 혜택도 만족스러움</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>매우 고급스러운 포장 — 은은하고 고급스러운 색상의 포장으로 선물 가치가 높음
-피부 상태 개선 체감 — 복용 후 피부가 한결 맑아지는 듯한 느낌을 체감함
-알찬 샘플 추가 구성 — 본품 외에 추가 샘플이 증정되어 만족도가 높음</t>
+          <t>고급스러운 예쁜 포장 — 은은한 핑크 색상과 오간자 포장이 매우 고급스러워 선물용으로 훌륭함
+피부 개선 체감 — 꾸준히 먹어보니 피부가 맑아지는 것 같은 느낌을 받음
+샘플 증정 구성 — 추가 샘플 구성이 함께 포함되어 만족스러운 혜택을 제공함</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 패키지 — 저렴한 가격에 풍성한 수량을 구매할 수 있어 경제적임
-질리지 않는 다양한 맛 — 메뉴가 다채롭고 양념이 자극적이지 않아 매일 먹기 좋음
-간편한 전자레인지 조리 — 전자레인지 조리로 다이어트 식단을 간편하게 해결할 수 있음</t>
+          <t>훌륭한 가성비와 맛 — 저렴한 가격 대비 다양한 양념과 뻑뻑하지 않은 맛으로 만족스러움
+간편한 전자레인지 조리 — 전자레인지 조리로 간편하게 식단 관리를 진행할 수 있음
+빠른 배송과 꼼꼼 포장 — 배송이 빠르고 꼼꼼하게 포장되어 지속적으로 재구매함</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 비리고 텁텁한 맛없이 일반 모카라떼나 초코우유처럼 맛있음
-부드러운 목넘김과 속 편안함 — 목넘김이 부드럽고 복용 후 속이 더부룩하지 않음
-휴대하기 편한 슬림 패키지 — 패키지가 슬림하여 가방에 넣어 다니며 챙겨 마시기 유용함</t>
+          <t>비린 맛 없는 깔끔함 — 단백질 음료 특유의 비리거나 텁텁한 맛없이 부드럽게 넘어감
+운동 후 포만감 및 영양 — 운동 후 단백질 보충용으로 좋고 속이 더부룩하지 않으며 허기 완화에 도움 됨
+우수한 휴대성 및 배송 — 슬림한 패키지로 들고 다니기 편하며 배송이 빠르게 진행됨</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>골라 먹는 다채로운 종류 — 다양한 종류로 구성되어 하나씩 골라 먹는 재미가 있음
-합리적인 할인 가격 — 알찬 패키지 구성을 저렴한 세일 가격으로 구매 가능함
-유용한 보냉파우치 증정 — 증정되는 보냉백이 도시락을 싸 다닐 때 요용함</t>
+          <t>다양한 종류와 뛰어난 맛 — 여러 맛이 구성되어 골라 먹는 재미가 있고 닭가슴살 맛이 좋음
+풍성한 할인 및 혜택 — 할인 가격과 보냉 파우치 증정 구성으로 가성비가 훌륭함
+간편한 식단 관리 — 아침이나 점심 도시락 대용으로 간편히 식단 관리가 가능함</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t>귀여운 키링 증정 혜택 — 함께 구성된 키링 증정품의 만족도가 매우 높음
-물이나 음료에 잘 섞임 — 물이나 음료에 타서 먹기 부담이 없고 간편함
-체감되는 운동 및 근육 효과 — 지속 섭취 시 몸이 커지고 득근하는 효과를 느낌</t>
+          <t>소화 및 배변 활동 개선 — 식후 속 더부룩함이 감소하고 배변 활동을 원활하게 도와줌
+고소한 군고구마 맛 — 군고구마 맛이 나며 고소하여 거부감 없이 맛있게 먹을 수 있음
+간편한 스틱 및 혜택 — 1포씩 개별 포장되어 간편하며 할인 이벤트 및 사은품 구성이 알참</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>고소한 군고구마 맛 — 군고구마 맛이 나며 부담 없이 맛있게 먹을 수 있음
-속 편한 소화 및 배변 도움 — 식후 더부룩함과 답답함이 줄어들고 배변 활동에 도움이 됨
-간편한 스틱 포장 — 한 포씩 포장되어 있어 가지고 다니며 챙겨 먹기 편함</t>
+          <t>섭취 편의성과 효과 — 물이나 음료에 쉽게 타 먹을 수 있고 운동 시 수행 능력 및 득근에 도움 됨
+귀여운 키링 증정 — 함께 제공되는 캐릭터 키링 사은품에 대한 만족도가 높음
+입문용 적합 용량 — 크레아틴을 처음 먹어보는 사람도 부담 없이 시작하기에 적절한 용량임</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>확실한 활력 및 체력 증진 — 초고함량 아르기닌 섭취로 체력, 지구력, 집중력 향상에 도움 됨
-편리한 1포 개별 포장 — 개별 포장되어 있어 휴대가 쉽고 하루 1포로 간편하게 섭취함
-선물용으로 우수한 패키지 — 고급스러운 포장 디자인과 쇼핑백이 함께 제공되어 선물용으로 제격임</t>
+          <t>초고함량 및 우수한 효과 — 1포당 L-아르기닌 6,200mg 함유로 운동 및 일상 활력 증진에 효과적임
+고급스러운 포장 패키지 — 블랙앤레드 패키지와 전용 쇼핑백, 추가 덤 증정으로 선물용으로 우수함
+간편한 개별 포장 — 하루 1포 스틱 제형으로 개별 포장되어 휴대가 편하고 복용이 간단함</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>체감되는 일상 피로 해소 — 섭취 후 아침에 몸이 가볍고 일상 피로가 줄어듦
-간편한 알약 제형 — 알약 형태로 되어 있어 매일 부담 없이 챙겨 먹기 편리함
-알찬 2개월분 세트 구성 — 아르기닌과 밀크씨슬(마카) 조합의 넉넉한 2개월분 구성이 만족스러움</t>
+          <t>챙겨 먹기 편한 알약 — 알약 제형으로 제작되어 매일 간편하게 영양을 챙길 수 있음
+시너지 알찬 구성 — 아르기닌과 밀크씨슬(마카) 조합으로 피로 완화 및 활력 관리에 유용함
+선물용 고급 쇼핑백 — 쇼핑백이 함께 포함되어 정성스러운 건강 선물용으로 적합함</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>피로 회복 및 운동 지원 — 아침 공복에 복용 시 가벼운 느낌이 들고 피로 회복과 운동에 도움이 됨
-부담 없는 레몬맛 액상 — 상큼한 레몬맛 액상이라 물에 타 먹거나 그냥 먹기 부담 없음
-외출 시 용이한 휴대성 — 액상 스틱 타입으로 외출할 때 간편히 챙기기 좋음</t>
+          <t>간편한 액상 스틱 — 액상 타입 스틱으로 물에 타 먹기 편하고 외출 시 휴대가 용이함
+상큼한 레몬 맛 — 레몬 맛으로 구성되어 거부감 없이 맛있게 복용 가능함
+활력 증진 및 피로 회복 — 아침 공복이나 운동 전에 먹으면 피로 회복과 에너지를 얻는 느낌임</t>
         </is>
       </c>
     </row>
@@ -4748,21 +4744,25 @@
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>굿즈 중심 구매 목적 — 효소 섭취보다는 굿즈 소장이 주 목적인 경우가 있음</t>
+        </is>
+      </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>즉각적 효과 확인의 한계 — 복용 초반에는 효과를 즉시 체감하기 어려움</t>
+          <t>단기간 효과 체감 미흡 — 섭취한 지 며칠 지나지 않아 즉각적인 효과 체감은 아직 어려움</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>배송 중 제품 해동 — 배송 시 제품이 완전히 녹아 도착하는 문제가 있음</t>
+          <t>제품 해동 배송 문제 — 배송 중 포장 내 제품이 전체적으로 녹아서 도착함</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>배송 시 상품 해동 문제 — 도착했을 때 제품이 많이 녹아 있는 경우가 있음</t>
+          <t>제품 해동 및 배송 문의 — 여름철 배송 시 많이 녹아서 오거나 사은품 별도 배송 여부 확인 필요함</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr"/>
@@ -4804,12 +4804,12 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
+          <t>46,900원</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
           <t>17,900원</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>46,900원</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5037,43 +5037,47 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032306284&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=032627034&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260805/e483TrUWUwCko9CBv1Da032306284_00_00e483TrUWUwCko9CBv1Da.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260810/jotmVom4KndGXbIlPcuj032627034_00_01jotmVom4KndGXbIlPcuj.jpg</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>64</v>
+        <v>1063</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>수면 질 개선 효과 — 새벽에 깨지 않고 숙면을 취하는 데 효과가 있음</t>
+          <t>쾌변 및 배변 도움 — 복용 후 화장실을 원활하게 가게 되어 편안함을 느낌</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>체중 유지 관리 도움 — 음식을 많이 섭취해도 체중이 증가하지 않도록 도와줌</t>
+          <t>뛰어난 가성비 — 다이소에서 저렴한 가격에 구매할 수 있어 높은 만족도를 제공함</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>편리한 복용 편의성 — 사용 방법이 간편하여 꾸준히 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>편리한 섭취 방식 — 섭취가 간편하여 지속적으로 복용하기 양호함</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>개인별 효과 체감 차이 — 사람에 따라 유행하는 제품 대비 명확한 효과를 체감하지 못할 수 있음</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -5081,48 +5085,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>종근당건강 관절연골엔 MSM 60정 30일분</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대웅제약</t>
+          <t>종근당건강</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000126&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581121&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/u8Kxfk5gV3uvRKBRNTM6600000126_00_00u8Kxfk5gV3uvRKBRNTM6.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260424/e7PvuolyW0jdoQAtpzxC591581121_00_01e7PvuolyW0jdoQAtpzxC.jpg</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3835</v>
+        <v>414</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 가격 대비 품질이 뛰어나 부담 없이 꾸준히 구매하기 좋음</t>
+          <t>관절 개선 기대감 — 관절과 무릎 건강 개선을 기대하며 꾸준히 챙겨 먹기 좋음</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>눈 건강 관리 도움 — 눈 건강을 챙기는 데 도움이 되어 꾸준히 섭취함</t>
+          <t>온라인 구매 편의성 — 매장에 재고가 부족한 제품을 다이소몰에서 편하게 주문 가능함</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>제약사 신뢰도 및 재구매 — 대웅제약 브랜드 신뢰도가 높아 지속해서 재구매함</t>
+          <t>타 영양제와 병용 용이 — 콘드로이친 등 다른 관절 영양제와 함께 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -5132,7 +5136,7 @@
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -5140,12 +5144,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>안국약품 브이팩 여성용 올인원 멀티 비타민 7포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>안국약품</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5155,35 +5159,31 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=968235548&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000144&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260402/05kyKLN3QpKvymmVHajT968235548_00_0005kyKLN3QpKvymmVHajT.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/OqDM0kpIHoqFD3okk28W600000144_00_00OqDM0kpIHoqFD3okk28W.png</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>328</v>
+        <v>6224</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>편리한 소포장 휴대성 — 소포장으로 구성되어 휴대하기 편하고 매일 잘 챙겨 먹게 됨</t>
+          <t>뛰어난 가성비 — 다이소 영양제 특유의 압도적인 가성비를 제공함</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>컨디션 회복 및 피로 개선 — 일주일 복용 후 컨디션이 좋아지고 피로감이 줄어듦</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>믿을 수 있는 제약사 상품 — 제약사 브랜드를 믿고 살 수 있으며 가성비가 훌륭함</t>
-        </is>
-      </c>
+          <t>무난한 꾸준 복용 — 부족한 영양을 채우기 위해 무난하게 계속 복용하기에 유용함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -5191,7 +5191,7 @@
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 마그마 스피드 30정</t>
+          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5214,43 +5214,51 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610910727&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911092&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20251111/69fT92p91uLANMODpyck610910727_00_0069fT92p91uLANMODpyck.png</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260814/qU3FUPerTqzVYxrqf7Lx610911092_00_01qU3FUPerTqzVYxrqf7Lx.jpg</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>362</v>
+        <v>53</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>리포좀 제형의 적절함 — 동국제약의 리포좀 스탈 제형으로 함량이 적당함</t>
+          <t>저렴한 메가도스 가격 — 메가도스용 비타민C를 저렴한 가격으로 구매할 수 있음</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>저렴하고 다양한 가성비 — 제품군이 다양하고 저렴하게 좋은 제품을 살 수 있음</t>
+          <t>개별 포장 편의성 — 포장이 1포씩 개별 구성되어 매일 간편하게 챙겨 먹기 편리함</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>다리 쥐 완화 효과 — 종아리에 쥐가 자주 나는 증상이 많이 개선됨</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+          <t>적은 속 쓰림 — 신맛에 비해 복용 후 속이 쓰리거나 힘들지 않아 만족스러움</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>가루 제형의 섭취 불편 — 가루 형태로 되어 있어 복용할 때 다소 먹기 힘들 수 있음</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>시중 가격 대비 비쌈 — 타 구매처에 비해 다이소 판매 가격이 상대적으로 비싸게 느껴짐</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
     </row>
     <row r="6" ht="38" customHeight="1">
       <c r="B6" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5258,12 +5266,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>종근당건강 관절연골엔 MSM 60정 30일분</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5273,35 +5281,27 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581121&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000127&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260424/e7PvuolyW0jdoQAtpzxC591581121_00_01e7PvuolyW0jdoQAtpzxC.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/V0qSVbLLgSaCWbYWEu73600000127_00_00V0qSVbLLgSaCWbYWEu73.png</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>413</v>
+        <v>2553</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>관절 및 무릎 관리 도움 — 불편한 관절과 무릎 건강 개선을 위해 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>전문가 추천 제품 신뢰 — 약사들이 추천하는 유명 브랜드 제품이라 믿음이 감</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>지속적인 복용 적합성 — 부담 없이 매일 꾸준히 먹을 수 있음</t>
-        </is>
-      </c>
+          <t>부담 없는 무난함 — 매월 지속해서 사서 복용하기에 부담 없고 무난한 비타민C임</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
@@ -5317,12 +5317,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 PDRN 필름 10매 10일분</t>
+          <t>대웅제약 MSM 90정 30일분</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대웅제약</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5332,43 +5332,43 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911098&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000149&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260728/2LpWqYu8CZWzex7rdnk8610911098_00_012LpWqYu8CZWzex7rdnk8.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/gVoECGdnaBQU8HtRPGFz600000149_00_00gVoECGdnaBQU8HtRPGFz.png</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J7" t="n">
-        <v>75</v>
+        <v>929</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>녹여 먹는 편한 필름 제형 — 알약이나 젤리보다 잘 녹아 복용하기가 매우 편리함</t>
+          <t>가격 대비 높은 성능 — 가격 대비 구성과 효과 면에서 높은 만족도를 줌</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>부담 없는 새콤한 맛 — 많이 달지 않고 새콤하여 맛있게 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>착한 가격과 뛰어난 품질 — 가격이 저렴하면서도 믿고 살 수 있는 품질임</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>영양제 구비의 용이성 — 다이소를 통해 각종 영양제를 쉽게 구할 수 있어 유용함</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>변색되어 보이는 외관 — 알약 색상이 누렇게 보여 초기 수령 시 변색된 듯한 오인을 줄 수 있음</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="B8" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5376,62 +5376,62 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>셀트리온</t>
+          <t>안국약품</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=944863413&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=985472642&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260605/8ADhx4mYwiTujsVcCSTD944863413_00_018ADhx4mYwiTujsVcCSTD.jpg</t>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250623/yivvMAKVS3Hyi026FPyX985472642_00_00yivvMAKVS3Hyi026FPyX.jpg</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2428</v>
+        <v>1907</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 커피맛 — 아메리카노처럼 고소하고 맛있어 외부 커피 대용으로 마시기 좋음</t>
+          <t>다이소의 뛰어난 가성비 — 이노시톨 영양제를 저렴한 가격으로 부담 없이 구할 수 있음</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>수면 방해 없는 섭취 — 마신 후에도 잠이 잘 와서 카페인 부담 없이 마실 수 있음</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>배변 활동 원활 도움 — 점심 식사 후 마시면 화장실을 잘 가게 됨</t>
-        </is>
-      </c>
+          <t>간편한 복용성 — 일상에서 편하게 막 먹기 좋아 접근성이 높음</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>아쉬운 체중 감량 효과 — 맛과 편의성은 좋으나 직접적인 다이어트 효과는 체감하기 어려움</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>아쉬운 제품 맛 — 1포당 양은 많으나 맛이 별로라 복용 시 아쉬움이 남음</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>모호한 체감 효과 — 다 먹은 후에도 확실한 효과 체감이 어려울 수 있음</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
     </row>
     <row r="9" ht="38" customHeight="1">
       <c r="B9" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5439,12 +5439,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5454,19 +5454,35 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=591581091&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651649&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260601/30NEHOm4dIOnmUVwUKLJ591581091_00_0030NEHOm4dIOnmUVwUKLJ.jpg</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/RN6BLb2wWdxkL0nu9aVK600651649_00_00RN6BLb2wWdxkL0nu9aVK.jpg</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1493</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>쾌변 및 장 건강 도움 — 복용 후 화장실 이용이 원활해지고 매일 상쾌함을 느낌</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>알약 캡슐의 편의성 — 캡슐 알약 형태라 아무 때나 간편하게 먹기 양호함</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>우수한 가성비 — 저렴한 가격 대비 장 건강을 챙길 수 있는 가성비 상품임</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
@@ -5474,7 +5490,7 @@
     <row r="10" ht="38" customHeight="1">
       <c r="B10" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5482,12 +5498,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
+          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5497,27 +5513,47 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=610911099&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600651650&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20260728/NbSqiy25P90IFlYxB3ux610911099_00_01NbSqiy25P90IFlYxB3ux.jpg</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>https://cdn.daisomall.co.kr/file/PD/20260325/wjBYMQTwSs5Uxawy8JxO600651650_00_00wjBYMQTwSs5Uxawy8JxO.jpg</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>555</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>목 넘김이 편한 작은 알약 — 알약 크기가 작은 편이라 목 넘김 부담 없이 꾸준히 복용 가능함</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>복용 중단 시 체감 효과 — 먹다 안 먹으면 차이가 확실히 체감될 정도로 효능이 양호함</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>좋은 성분과 품질 — 성분이 양호하고 지속 재구매할 정도로 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>상대적으로 높은 가격 — 다이소 내 매장 상품 기준으로는 가격이 다소 비싸게 느껴짐</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5525,7 +5561,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 글루타치온 30정 30일분</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5535,25 +5571,45 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000132&amp;recmYn=N</t>
+          <t>https://www.daisomall.co.kr/pd/pdr/SCR_PDR_0001?pdNo=600000130&amp;recmYn=N</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://cdn.daisomall.co.kr/file/PD/20250408/SvY5chCvz0QZIyP7AdTc600000132_00_00SvY5chCvz0QZIyP7AdTc.png</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>https://cdn.daisomall.co.kr/file/PD/20250408/0tJFRHjUfKCxN5mKhDV0600000130_00_000tJFRHjUfKCxN5mKhDV0.png</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1469</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>캔디형 제형의 편의성 — 캔디형 제형으로 녹여 먹거나 씹어 먹기 편함</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>피부 톤 개선 효과 — 비타민C와 함께 복용 시 피부 톤이 밝아지는 느낌을 받음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>쾌변 등 부가 효과 — 비타민과 복용 시 예상외로 배변 활동 완화에 도움을 받음</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>초기 효과 체감 미흡 — 복용 초기에는 명확한 효과를 바로 확인하기 어려울 수 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -5673,47 +5729,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>혈행</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>프로바이오틱스/유산균</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>비타민D</t>
         </is>
       </c>
     </row>
@@ -5725,47 +5781,47 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿</t>
+          <t>자연관</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>종근당건강</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>대웅제약</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>동국제약</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>대웅제약</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>안국약품</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>종근당건강</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>동국제약</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>셀트리온</t>
-        </is>
-      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>종근당건강</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>유한양행</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -5782,52 +5838,52 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>닥터블릿 푸응 7 Days 슬립앤버닝 14정 7일분</t>
+          <t>자연관 이지슬로 엑스트라버진 올리브오일＆레몬 4병</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 루테인 30정 30일분</t>
+          <t>종근당건강 관절연골엔 MSM 60정 30일분</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>안국약품 브이팩 여성용 올인원 멀티 비타민 7포</t>
+          <t>대웅제약 코엔자임 Q10 30캡슐 30일분</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>동국제약 리포좀 마그마 스피드 30정</t>
+          <t>[신혜선 PICK] 동국제약 프라임도스 비타민C 2000 30포 30일분</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>종근당건강 관절연골엔 MSM 60정 30일분</t>
+          <t>대웅제약 비타민C 30정 30일분</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 PDRN 필름 10매 10일분</t>
+          <t>대웅제약 MSM 90정 30일분</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>[다영 PICK] 셀트리온 다이어트 한 잔 슬림 S 프레소 10포 5일분</t>
+          <t>안국약품 콜린 미오이노시톨 4000 10포</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>[김우빈 PICK] 종근당건강 아임비타 비타민B 2000 30정 30일분</t>
+          <t>유한양행 장건강 생유산균 30캡슐 30일분</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>[신혜선 PICK] 동국제약 마데카 글루타치온 필름 12매 12일분</t>
+          <t>유한양행 비피더스 생유산균 10캡슐 10일분</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>대웅제약 비타민D 4000IU 30정 30일분</t>
+          <t>대웅제약 글루타치온 30정 30일분</t>
         </is>
       </c>
     </row>
@@ -5841,7 +5897,7 @@
         <v>4.8</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>4.8</v>
@@ -5850,17 +5906,23 @@
         <v>4.7</v>
       </c>
       <c r="G6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L6" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="H6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="B7" s="1" t="inlineStr">
@@ -5869,29 +5931,35 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>64</v>
+        <v>1063</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>3835</v>
+        <v>414</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>328</v>
+        <v>6224</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>362</v>
+        <v>53</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>413</v>
+        <v>2553</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>75</v>
+        <v>929</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>2428</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
+        <v>1907</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>1493</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>555</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>1469</v>
+      </c>
     </row>
     <row r="8" ht="90" customHeight="1">
       <c r="B8" s="1" t="inlineStr">
@@ -5901,77 +5969,112 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>수면 질 개선 효과 — 새벽에 깨지 않고 숙면을 취하는 데 효과가 있음
-체중 유지 관리 도움 — 음식을 많이 섭취해도 체중이 증가하지 않도록 도와줌
-편리한 복용 편의성 — 사용 방법이 간편하여 꾸준히 챙겨 먹기 좋음</t>
+          <t>쾌변 및 배변 도움 — 복용 후 화장실을 원활하게 가게 되어 편안함을 느낌
+뛰어난 가성비 — 다이소에서 저렴한 가격에 구매할 수 있어 높은 만족도를 제공함
+편리한 섭취 방식 — 섭취가 간편하여 지속적으로 복용하기 양호함</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>부담 없는 가성비 — 가격 대비 품질이 뛰어나 부담 없이 꾸준히 구매하기 좋음
-눈 건강 관리 도움 — 눈 건강을 챙기는 데 도움이 되어 꾸준히 섭취함
-제약사 신뢰도 및 재구매 — 대웅제약 브랜드 신뢰도가 높아 지속해서 재구매함</t>
+          <t>관절 개선 기대감 — 관절과 무릎 건강 개선을 기대하며 꾸준히 챙겨 먹기 좋음
+온라인 구매 편의성 — 매장에 재고가 부족한 제품을 다이소몰에서 편하게 주문 가능함
+타 영양제와 병용 용이 — 콘드로이친 등 다른 관절 영양제와 함께 챙겨 먹기 적합함</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>편리한 소포장 휴대성 — 소포장으로 구성되어 휴대하기 편하고 매일 잘 챙겨 먹게 됨
-컨디션 회복 및 피로 개선 — 일주일 복용 후 컨디션이 좋아지고 피로감이 줄어듦
-믿을 수 있는 제약사 상품 — 제약사 브랜드를 믿고 살 수 있으며 가성비가 훌륭함</t>
+          <t>뛰어난 가성비 — 다이소 영양제 특유의 압도적인 가성비를 제공함
+무난한 꾸준 복용 — 부족한 영양을 채우기 위해 무난하게 계속 복용하기에 유용함</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>리포좀 제형의 적절함 — 동국제약의 리포좀 스탈 제형으로 함량이 적당함
-저렴하고 다양한 가성비 — 제품군이 다양하고 저렴하게 좋은 제품을 살 수 있음
-다리 쥐 완화 효과 — 종아리에 쥐가 자주 나는 증상이 많이 개선됨</t>
+          <t>저렴한 메가도스 가격 — 메가도스용 비타민C를 저렴한 가격으로 구매할 수 있음
+개별 포장 편의성 — 포장이 1포씩 개별 구성되어 매일 간편하게 챙겨 먹기 편리함
+적은 속 쓰림 — 신맛에 비해 복용 후 속이 쓰리거나 힘들지 않아 만족스러움</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>관절 및 무릎 관리 도움 — 불편한 관절과 무릎 건강 개선을 위해 챙겨 먹기 좋음
-전문가 추천 제품 신뢰 — 약사들이 추천하는 유명 브랜드 제품이라 믿음이 감
-지속적인 복용 적합성 — 부담 없이 매일 꾸준히 먹을 수 있음</t>
+          <t>부담 없는 무난함 — 매월 지속해서 사서 복용하기에 부담 없고 무난한 비타민C임</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>녹여 먹는 편한 필름 제형 — 알약이나 젤리보다 잘 녹아 복용하기가 매우 편리함
-부담 없는 새콤한 맛 — 많이 달지 않고 새콤하여 맛있게 먹기 좋음
-착한 가격과 뛰어난 품질 — 가격이 저렴하면서도 믿고 살 수 있는 품질임</t>
+          <t>가격 대비 높은 성능 — 가격 대비 구성과 효과 면에서 높은 만족도를 줌
+영양제 구비의 용이성 — 다이소를 통해 각종 영양제를 쉽게 구할 수 있어 유용함</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>고소하고 맛있는 커피맛 — 아메리카노처럼 고소하고 맛있어 외부 커피 대용으로 마시기 좋음
-수면 방해 없는 섭취 — 마신 후에도 잠이 잘 와서 카페인 부담 없이 마실 수 있음
-배변 활동 원활 도움 — 점심 식사 후 마시면 화장실을 잘 가게 됨</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
+          <t>다이소의 뛰어난 가성비 — 이노시톨 영양제를 저렴한 가격으로 부담 없이 구할 수 있음
+간편한 복용성 — 일상에서 편하게 막 먹기 좋아 접근성이 높음</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>쾌변 및 장 건강 도움 — 복용 후 화장실 이용이 원활해지고 매일 상쾌함을 느낌
+알약 캡슐의 편의성 — 캡슐 알약 형태라 아무 때나 간편하게 먹기 양호함
+우수한 가성비 — 저렴한 가격 대비 장 건강을 챙길 수 있는 가성비 상품임</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>목 넘김이 편한 작은 알약 — 알약 크기가 작은 편이라 목 넘김 부담 없이 꾸준히 복용 가능함
+복용 중단 시 체감 효과 — 먹다 안 먹으면 차이가 확실히 체감될 정도로 효능이 양호함
+좋은 성분과 품질 — 성분이 양호하고 지속 재구매할 정도로 만족도가 높음</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>캔디형 제형의 편의성 — 캔디형 제형으로 녹여 먹거나 씹어 먹기 편함
+피부 톤 개선 효과 — 비타민C와 함께 복용 시 피부 톤이 밝아지는 느낌을 받음
+쾌변 등 부가 효과 — 비타민과 복용 시 예상외로 배변 활동 완화에 도움을 받음</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>개인별 효과 체감 차이 — 사람에 따라 유행하는 제품 대비 명확한 효과를 체감하지 못할 수 있음</t>
+        </is>
+      </c>
       <c r="D9" s="3" t="inlineStr"/>
       <c r="E9" s="3" t="inlineStr"/>
-      <c r="F9" s="3" t="inlineStr"/>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>가루 제형의 섭취 불편 — 가루 형태로 되어 있어 복용할 때 다소 먹기 힘들 수 있음
+시중 가격 대비 비쌈 — 타 구매처에 비해 다이소 판매 가격이 상대적으로 비싸게 느껴짐</t>
+        </is>
+      </c>
       <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>변색되어 보이는 외관 — 알약 색상이 누렇게 보여 초기 수령 시 변색된 듯한 오인을 줄 수 있음</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>아쉬운 체중 감량 효과 — 맛과 편의성은 좋으나 직접적인 다이어트 효과는 체감하기 어려움</t>
+          <t>아쉬운 제품 맛 — 1포당 양은 많으나 맛이 별로라 복용 시 아쉬움이 남음
+모호한 체감 효과 — 다 먹은 후에도 확실한 효과 체감이 어려울 수 있음</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>상대적으로 높은 가격 — 다이소 내 매장 상품 기준으로는 가격이 다소 비싸게 느껴짐</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>초기 효과 체감 미흡 — 복용 초기에는 명확한 효과를 바로 확인하기 어려울 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -5986,7 +6089,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -6011,7 +6114,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -6026,7 +6129,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>3,000원</t>
+          <t>5,000원</t>
         </is>
       </c>
     </row>
@@ -6240,11 +6343,11 @@
         <v>4.9</v>
       </c>
       <c r="J2" t="n">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>올영세일 대표 쟁임템 — 올리브영 세일 기간에 구매하여 건강을 챙기기 좋은 제품임</t>
+          <t>직장인 추천 이너뷰티 — 피곤한 직장인에게 올영세일 기간 쟁여두기 좋은 건강 제품임</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -6256,7 +6359,7 @@
     <row r="3" ht="38" customHeight="1">
       <c r="B3" t="inlineStr">
         <is>
-          <t>비타민C/항산화</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -6264,58 +6367,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
+          <t>세노비스 마그네슘 180정 기획 (6개월분)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>고려은단</t>
+          <t>세노비스</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9,900원</t>
+          <t>27,900원</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258054&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=2</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025805404ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>5586</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>체감되는 피로 개선 효과 — 고용량 비타민C 복용으로 피로도 체감이 크게 달라짐</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>높은 만족도의 정착템 — 복용 후 컨디션 유지에 만족도가 높아 지속해서 정착하게 됨</t>
-        </is>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>강한 신맛의 자극 — 가루 제형 특성상 신맛이 다소 강하게 느껴질 수 있음</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
     </row>
     <row r="4" ht="38" customHeight="1">
       <c r="B4" t="inlineStr">
         <is>
-          <t>피부/미용</t>
+          <t>비타민C/항산화</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -6323,46 +6414,66 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>닥터아돌 B발라민 비오틴 120정 (2개월분)</t>
+          <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>닥터아돌</t>
+          <t>고려은단</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>30,600원</t>
+          <t>9,900원</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000231625&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000187268&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=3</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023162516ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0018/A00000018726811ko.png?l=ko</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="J4" t="n">
-        <v>30</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>5597</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>피로 회복 체감 효과 — 고용량 섭취 후 피로도 체감이 크게 개선됨을 확인하게 됨</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>지속적인 재구매 정착 — 가족들과 함께 수년간 지속 재구매하며 정착하기 양호함</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>올영세일 추천템 — 올리브영 세일 할인 혜택으로 구매하기에 적절함</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>강한 신맛의 자극 — 비타민C 고용량 특성상 신맛이 꽤 강하게 느껴짐</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>충분한 수물 섭취 필요 — 결석 방지를 위해 하루 2L 이상의 충분한 수분 섭취가 요구됨</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="B5" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6370,7 +6481,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>세노비스 마그네슘 180정 기획 (6개월분)</t>
+          <t>세노비스 밀크씨슬 120캡슐 선물세트 (4개월분)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -6380,24 +6491,24 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>27,900원</t>
+          <t>24,800원</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000258054&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000232629&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=4</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0025/A00000025805404ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023262901ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>4.9</v>
       </c>
       <c r="J5" t="n">
-        <v>200</v>
+        <v>1260</v>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -6444,21 +6555,21 @@
         <v>4.9</v>
       </c>
       <c r="J6" t="n">
-        <v>15381</v>
+        <v>15388</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>비타민C와 D의 복합 케어 — 면역 관리를 위한 비타민C와 실내 생활에 필요한 비타민D를 함께 챙김</t>
+          <t>비타민 C와 D 올인원 — 면역력의 비타민C와 실내 생활 필수인 비타민D를 함께 케어함</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>꾸준한 에너지 관리 — 부족한 에너지를 채워주어 오랫동안 정착하여 복용하기 좋음</t>
+          <t>높은 가성비와 브랜드 신뢰 — 고려은단 브랜드 가치 대비 가성비와 효과가 양호함</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>고려은단 브랜드 가성비 — 믿을 수 있는 품질과 뛰어난 가성비를 제공함</t>
+          <t>꾸준한 이너뷰티 루틴 — 운동 및 일상생활 중 지속해서 챙겨 먹으며 건강 관리에 도움 됨</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -6468,7 +6579,7 @@
     <row r="7" ht="38" customHeight="1">
       <c r="B7" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>피부/미용</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6476,38 +6587,50 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
+          <t>[산리오캐릭터즈에디션/9월올영픽] 비비랩 화이트 콜라겐 18포 기획 (+2포) (+헬로키티 마켓백)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>바이오코어유산균</t>
+          <t>비비랩</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>12,500원</t>
+          <t>11,900원</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248072&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=6</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014346ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024807232ko.png?l=ko</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J7" t="n">
-        <v>12356</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>2105</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>맛있는 복숭아 맛 — 자두사탕 느낌의 복숭아 맛으로 거부감 없이 맛있게 복용할 수 있음</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>저분자 콜라겐 함량 강화 — 기존 대비 2배 강화된 2,400mg 저분자 콜라겐을 한 포에 담음</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>올영세일 필수 재구매 — 피부 속 광채와 이너뷰티 케어를 위해 올영세일에 쟁이기 좋음</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
@@ -6523,50 +6646,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[산리오캐릭터즈에디션/9월올영픽] 비비랩 화이트 콜라겐 18포 기획 (+2포) (+헬로키티 마켓백)</t>
+          <t>닥터아돌 B발라민 비오틴 120정 (2개월분)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>비비랩</t>
+          <t>닥터아돌</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>11,900원</t>
+          <t>30,600원</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000248072&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000231625&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A00000024807232ko.png?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0023/A00000023162516ko.png?l=ko</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2100</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>맛있는 복숭아맛 제형 — 자두사탕 느낌의 복숭아맛이라 거부감 없이 챙겨 먹기 좋음</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>높은 저분자 콜라겐 함량 — 저분자 콜라겐 함량이 높아 속부터 화사한 피부 관리에 도움이 됨</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>매력적인 산리오 굿즈 — 헬로키티 마켓백 등 귀여운 기획 굿즈가 함께 제공됨</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -6609,16 +6720,16 @@
         <v>4.9</v>
       </c>
       <c r="J9" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>소장 가치 높은 캐릭터 콜라보 — 헬로키티 굿즈와 스티커 구성으로 만족도가 높음</t>
+          <t>귀여운 캐릭터 굿즈 — 헬로키티 콜라보 굿즈가 포함되어 높은 만족감과 소장 가치를 줌</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>아이들도 좋아하는 구미 제형 — 맛있는 젤리 제형이라 아이들과 함께 즐기기 적합함</t>
+          <t>아이들과 나누기 좋은 구미 — 젤리 제형으로 아이들이나 친구들과 나누어 먹기 편함</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
@@ -6637,46 +6748,62 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[9월 올영픽] 락토핏 슬림 30포 트리플 기획 (+쿠로미 카드케이스) (45일분)</t>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>락토핏</t>
+          <t>멜라메이트</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24,400원</t>
+          <t>15,900원</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000263766&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000223554&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=9</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0026/A00000026376639ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0022/A00000022355477ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>7676</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>14821</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>빠르고 깊은 숙면 도움 — 섭취 후 뒤척임 없이 빠르고 푹 잘 수 있게 유도해 줌</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>맛있는 젤리 제형 — 알약 대신 맛있는 젤리로 구성되어 자기 전 부담 없이 먹을 수 있음</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>식물성 원료의 신뢰 — 식물성 멜라토닌 성분을 사용하여 믿고 안심하며 복용함</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>양치 후 복용의 불편함 — 젤리 제형 특성상 자기 전 복용 시 양치를 다시 해야 하는 귀찮음이 있음</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
     </row>
     <row r="11" ht="38" customHeight="1">
       <c r="B11" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -6684,47 +6811,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
+          <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>아임비타</t>
+          <t>바이오코어유산균</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24,900원</t>
+          <t>12,500원</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000249166&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
+          <t>https://www.oliveyoung.co.kr/store/goods/getGoodsDetail.do?goodsNo=A000000200143&amp;dispCatNo=90000010009&amp;trackingCd=Best_Sellingbest&amp;t_page=%EB%9E%AD%ED%82%B9&amp;t_click=%ED%8C%90%EB%A7%A4%EB%9E%AD%ED%82%B9_%EA%B1%B4%EA%B0%95%EC%8B%9D%ED%92%88_%EC%83%81%ED%92%88%EC%83%81%EC%84%B8&amp;t_number=10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0024/A000000249166123ko.jpg?l=ko</t>
+          <t>https://image.oliveyoung.co.kr/cfimages/cf-goods/uploads/images/thumbnails/400/10/0000/0020/A00000020014346ko.jpg?l=ko</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>10921</v>
+        <v>12363</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>즐겨 먹는 이뮨 비타민 — 피로할 때 즐겨 마시는 대표 멀티비타민 제품임</t>
+          <t>귀여운 캐릭터 굿즈 — 산리오 러기지택 굿즈가 포함되어 귀엽고 세일가 구매에 적합함</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>포차코 메쉬백 증정 혜택 — 귀여운 포차코 메쉬백 증정이 포함되어 구매 만족도가 높음</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>장 건강 및 속 편안함 — 배 아픔이나 가스 참 없이 속이 편안하고 화장실 이용을 돕음</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>피부 면역 동시 케어 — 장 건강뿐만 아니라 피부 면역 개선 효과까지 함께 기대 가능함</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 기존 제품들에 비해 캡슐/알약 크기가 다소 크게 느껴질 수 있음</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
     </row>
@@ -6844,47 +6979,47 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
+          <t>마그네슘</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>비타민C/항산화</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>피부/미용</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>마그네슘</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>피부/미용</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>비타민C/항산화</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>기타/특수목적</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>다이어트/체중관리</t>
-        </is>
-      </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>피부/미용</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>비타민C/항산화</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>기타/특수목적</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
     </row>
@@ -6901,47 +7036,47 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>세노비스</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>고려은단</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>세노비스</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>고려은단</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>비비랩</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>닥터아돌</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>세노비스</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>고려은단</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>올더베러</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>멜라메이트</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>바이오코어유산균</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>비비랩</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>올더베러</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>락토핏</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>아임비타</t>
         </is>
       </c>
     </row>
@@ -6958,47 +7093,47 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>세노비스 마그네슘 180정 기획 (6개월분)</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>[9월 올영픽] 고려은단 메가도스C 비타민C 3000mg 30포 (+헬로키티 파우치)</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>세노비스 밀크씨슬 120캡슐 선물세트 (4개월분)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>[산리오캐릭터즈에디션/9월올영픽] 비비랩 화이트 콜라겐 18포 기획 (+2포) (+헬로키티 마켓백)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>닥터아돌 B발라민 비오틴 120정 (2개월분)</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>세노비스 마그네슘 180정 기획 (6개월분)</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 고려은단 비타민C1000 이지+비타민D 120정 (+마이멜로디 파우치) (60일분)</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>[산리오 에디션] 올더베러 비타민C 구미 60구미 (30일분)(+헬로키티 카드스티커)</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>[감자숭이 기획] 멜라메이트 구미/로우슈가/버라이어티팩 구미 20/40/50구미</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>[9월 올영픽/산리오콜라보] CJ 바이오코어 유산균 3종 (피부/다이어트/500억) (+산리오 러기지택)</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>[산리오캐릭터즈에디션/9월올영픽] 비비랩 화이트 콜라겐 18포 기획 (+2포) (+헬로키티 마켓백)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>[산리오 에디션] 올더베러 비타민C 구미 60구미 (30일분)(+헬로키티 카드스티커)</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽] 락토핏 슬림 30포 트리플 기획 (+쿠로미 카드케이스) (45일분)</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>[9월 올영픽/김우빈PICK] 아임비타 멀티비타민 이뮨샷 12입 (+포차코 메쉬백) (12일분)</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7150,7 @@
         <v>4.9</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>4.9</v>
@@ -7024,10 +7159,10 @@
         <v>4.9</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>4.9</v>
@@ -7036,7 +7171,7 @@
         <v>4.8</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -7046,34 +7181,34 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>5586</v>
+        <v>200</v>
       </c>
       <c r="E7" s="3" t="n">
+        <v>5597</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1260</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>15388</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>2105</v>
+      </c>
+      <c r="I7" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>200</v>
-      </c>
-      <c r="G7" s="3" t="n">
-        <v>15381</v>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>12356</v>
-      </c>
-      <c r="I7" s="3" t="n">
-        <v>2100</v>
-      </c>
       <c r="J7" s="3" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>7676</v>
+        <v>14821</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>10921</v>
+        <v>12363</v>
       </c>
     </row>
     <row r="8" ht="90" customHeight="1">
@@ -7084,66 +7219,83 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>올영세일 대표 쟁임템 — 올리브영 세일 기간에 구매하여 건강을 챙기기 좋은 제품임</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>체감되는 피로 개선 효과 — 고용량 비타민C 복용으로 피로도 체감이 크게 달라짐
-높은 만족도의 정착템 — 복용 후 컨디션 유지에 만족도가 높아 지속해서 정착하게 됨</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr"/>
+          <t>직장인 추천 이너뷰티 — 피곤한 직장인에게 올영세일 기간 쟁여두기 좋은 건강 제품임</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>피로 회복 체감 효과 — 고용량 섭취 후 피로도 체감이 크게 개선됨을 확인하게 됨
+지속적인 재구매 정착 — 가족들과 함께 수년간 지속 재구매하며 정착하기 양호함
+올영세일 추천템 — 올리브영 세일 할인 혜택으로 구매하기에 적절함</t>
+        </is>
+      </c>
       <c r="F8" s="3" t="inlineStr"/>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>비타민C와 D의 복합 케어 — 면역 관리를 위한 비타민C와 실내 생활에 필요한 비타민D를 함께 챙김
-꾸준한 에너지 관리 — 부족한 에너지를 채워주어 오랫동안 정착하여 복용하기 좋음
-고려은단 브랜드 가성비 — 믿을 수 있는 품질과 뛰어난 가성비를 제공함</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>맛있는 복숭아맛 제형 — 자두사탕 느낌의 복숭아맛이라 거부감 없이 챙겨 먹기 좋음
-높은 저분자 콜라겐 함량 — 저분자 콜라겐 함량이 높아 속부터 화사한 피부 관리에 도움이 됨
-매력적인 산리오 굿즈 — 헬로키티 마켓백 등 귀여운 기획 굿즈가 함께 제공됨</t>
-        </is>
-      </c>
+          <t>비타민 C와 D 올인원 — 면역력의 비타민C와 실내 생활 필수인 비타민D를 함께 케어함
+높은 가성비와 브랜드 신뢰 — 고려은단 브랜드 가치 대비 가성비와 효과가 양호함
+꾸준한 이너뷰티 루틴 — 운동 및 일상생활 중 지속해서 챙겨 먹으며 건강 관리에 도움 됨</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>맛있는 복숭아 맛 — 자두사탕 느낌의 복숭아 맛으로 거부감 없이 맛있게 복용할 수 있음
+저분자 콜라겐 함량 강화 — 기존 대비 2배 강화된 2,400mg 저분자 콜라겐을 한 포에 담음
+올영세일 필수 재구매 — 피부 속 광채와 이너뷰티 케어를 위해 올영세일에 쟁이기 좋음</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr"/>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>소장 가치 높은 캐릭터 콜라보 — 헬로키티 굿즈와 스티커 구성으로 만족도가 높음
-아이들도 좋아하는 구미 제형 — 맛있는 젤리 제형이라 아이들과 함께 즐기기 적합함</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr"/>
+          <t>귀여운 캐릭터 굿즈 — 헬로키티 콜라보 굿즈가 포함되어 높은 만족감과 소장 가치를 줌
+아이들과 나누기 좋은 구미 — 젤리 제형으로 아이들이나 친구들과 나누어 먹기 편함</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>빠르고 깊은 숙면 도움 — 섭취 후 뒤척임 없이 빠르고 푹 잘 수 있게 유도해 줌
+맛있는 젤리 제형 — 알약 대신 맛있는 젤리로 구성되어 자기 전 부담 없이 먹을 수 있음
+식물성 원료의 신뢰 — 식물성 멜라토닌 성분을 사용하여 믿고 안심하며 복용함</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>즐겨 먹는 이뮨 비타민 — 피로할 때 즐겨 마시는 대표 멀티비타민 제품임
-포차코 메쉬백 증정 혜택 — 귀여운 포차코 메쉬백 증정이 포함되어 구매 만족도가 높음</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
+          <t>귀여운 캐릭터 굿즈 — 산리오 러기지택 굿즈가 포함되어 귀엽고 세일가 구매에 적합함
+장 건강 및 속 편안함 — 배 아픔이나 가스 참 없이 속이 편안하고 화장실 이용을 돕음
+피부 면역 동시 케어 — 장 건강뿐만 아니라 피부 면역 개선 효과까지 함께 기대 가능함</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="60" customHeight="1">
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>부정리뷰</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr"/>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>강한 신맛의 자극 — 가루 제형 특성상 신맛이 다소 강하게 느껴질 수 있음</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr"/>
+      <c r="D9" s="3" t="inlineStr"/>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>강한 신맛의 자극 — 비타민C 고용량 특성상 신맛이 꽤 강하게 느껴짐
+충분한 수물 섭취 필요 — 결석 방지를 위해 하루 2L 이상의 충분한 수분 섭취가 요구됨</t>
+        </is>
+      </c>
       <c r="F9" s="3" t="inlineStr"/>
       <c r="G9" s="3" t="inlineStr"/>
       <c r="H9" s="3" t="inlineStr"/>
       <c r="I9" s="3" t="inlineStr"/>
       <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>양치 후 복용의 불편함 — 젤리 제형 특성상 자기 전 복용 시 양치를 다시 해야 하는 귀찮음이 있음</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>다소 큰 알약 크기 — 기존 제품들에 비해 캡슐/알약 크기가 다소 크게 느껴질 수 있음</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="1" t="inlineStr">
@@ -7158,47 +7310,47 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
+          <t>27,900원</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
           <t>9,900원</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>24,800원</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>10,900원</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>11,900원</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>30,600원</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>27,900원</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>10,900원</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>8,900원</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>15,900원</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>12,500원</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>11,900원</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>8,900원</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>24,400원</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>24,900원</t>
         </is>
       </c>
     </row>
@@ -7286,7 +7438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7324,7 +7476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>멀티비타민/종합비타민</t>
+          <t>기타/특수목적</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -7334,32 +7486,32 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>기타/특수목적</t>
+          <t>다이어트/체중관리</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
@@ -7368,23 +7520,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>다이어트/체중관리</t>
+          <t>멀티비타민/종합비타민</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7394,16 +7546,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>7.5</v>
+        <v>12.5</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -7434,7 +7586,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루테인/눈건강</t>
+          <t>프로바이오틱스/유산균</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -7447,16 +7599,16 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>마그네슘</t>
+          <t>홍삼/인삼</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -7466,19 +7618,19 @@
         <v>2.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>홍삼/인삼</t>
+          <t>마그네슘</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -7488,19 +7640,19 @@
         <v>2.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>비타민D</t>
+          <t>루테인/눈건강</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -7513,9 +7665,31 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>혈행</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
         <v>0</v>
       </c>
     </row>
